--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_199_R20.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_199_R20.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>N. WEILER-BABB</t>
+          <t>J. LOYD</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5688</v>
+        <v>2.7853</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8974</v>
+        <v>1.6085</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6714</v>
+        <v>1.1768</v>
       </c>
       <c r="G2" t="n">
-        <v>1.7704</v>
+        <v>1.0664</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1141</v>
+        <v>0.7251</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6562</v>
+        <v>0.3413</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9138</v>
+        <v>2.2817</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6722</v>
+        <v>1.462</v>
       </c>
       <c r="L2" t="n">
-        <v>2.2416</v>
+        <v>0.8196</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.1434</v>
+        <v>-1.2152</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5581</v>
+        <v>-0.7369</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5854</v>
+        <v>-0.4783</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.5515</v>
+        <v>-1.1598</v>
       </c>
       <c r="R2" t="n">
-        <v>3.0154</v>
+        <v>2.3195</v>
       </c>
       <c r="S2" t="n">
-        <v>2.0124</v>
+        <v>-0.5131</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5351</v>
+        <v>-0.5856</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4774</v>
+        <v>0.0725</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.6778999999999999</v>
+        <v>1.0722</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. LOYD</t>
+          <t>N. WEILER-BABB</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4822</v>
+        <v>2.3063</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3726</v>
+        <v>0.0717</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1096</v>
+        <v>2.2345</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0664</v>
+        <v>1.7704</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7251</v>
+        <v>0.1141</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3413</v>
+        <v>1.6562</v>
       </c>
       <c r="J3" t="n">
-        <v>2.2817</v>
+        <v>2.9138</v>
       </c>
       <c r="K3" t="n">
-        <v>1.462</v>
+        <v>0.6722</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8196</v>
+        <v>2.2416</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.2152</v>
+        <v>-1.1434</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7369</v>
+        <v>-0.5581</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4783</v>
+        <v>-0.5854</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1598</v>
+        <v>-2.5515</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3195</v>
+        <v>3.0154</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8162</v>
+        <v>0.7499</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8215</v>
+        <v>-0.2906</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0053</v>
+        <v>1.0405</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0722</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5354</v>
+        <v>2.1245</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1945</v>
+        <v>0.1593</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7299</v>
+        <v>1.9652</v>
       </c>
       <c r="G4" t="n">
         <v>-1.2118</v>
@@ -766,13 +766,13 @@
         <v>3.0154</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.539</v>
+        <v>0.0501</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.187</v>
+        <v>-0.8331</v>
       </c>
       <c r="U4" t="n">
-        <v>0.648</v>
+        <v>0.8832</v>
       </c>
       <c r="V4" t="n">
         <v>2.8223</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1984</v>
+        <v>1.1654</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4217</v>
+        <v>0.6576</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7766999999999999</v>
+        <v>0.5079</v>
       </c>
       <c r="G5" t="n">
         <v>1.0358</v>
@@ -844,13 +844,13 @@
         <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3945</v>
+        <v>0.3615</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4481</v>
+        <v>-0.2122</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8426</v>
+        <v>0.5737</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. SMITS</t>
+          <t>K. JONES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0934</v>
+        <v>0.9384</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2767</v>
+        <v>0.6297</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8167</v>
+        <v>0.3087</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.5935</v>
+        <v>0.6397</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2435</v>
+        <v>0.5894</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.837</v>
+        <v>0.0502</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.8429</v>
+        <v>0.6218</v>
       </c>
       <c r="K6" t="n">
-        <v>0.78</v>
+        <v>0.6218</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.6229</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7504999999999999</v>
+        <v>0.0179</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5365</v>
+        <v>-0.0323</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.214</v>
+        <v>0.0502</v>
       </c>
       <c r="P6" t="n">
-        <v>2.0876</v>
+        <v>0.232</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0876</v>
+        <v>0.232</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7411</v>
+        <v>0.0668</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0474</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6937</v>
+        <v>0.0589</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. JONES</t>
+          <t>R. SMITS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9384</v>
+        <v>0.5715</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6297</v>
+        <v>-0.0771</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3087</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6397</v>
+        <v>-1.5935</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5894</v>
+        <v>0.2435</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0502</v>
+        <v>-1.837</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6218</v>
+        <v>-0.8429</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6218</v>
+        <v>0.78</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-1.6229</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0179</v>
+        <v>-0.7504999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0323</v>
+        <v>-0.5365</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0502</v>
+        <v>-0.214</v>
       </c>
       <c r="P7" t="n">
-        <v>0.232</v>
+        <v>2.0876</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.232</v>
+        <v>2.0876</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0668</v>
+        <v>0.2192</v>
       </c>
       <c r="T7" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.3064</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0589</v>
+        <v>0.5256</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.543</v>
+        <v>-0.1898</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1996</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3434</v>
+        <v>-0.1082</v>
       </c>
       <c r="G8" t="n">
         <v>0.8257</v>
@@ -1078,13 +1078,13 @@
         <v>0.6959</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7631</v>
+        <v>-0.4099</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2908</v>
+        <v>-0.1729</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4722</v>
+        <v>-0.237</v>
       </c>
       <c r="V8" t="n">
         <v>-0.1418</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8529</v>
+        <v>-1.8193</v>
       </c>
       <c r="E9" t="n">
         <v>-0.0211</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.8318</v>
+        <v>-1.7982</v>
       </c>
       <c r="G9" t="n">
         <v>-0.2825</v>
@@ -1156,13 +1156,13 @@
         <v>0.232</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0523</v>
+        <v>-0.0187</v>
       </c>
       <c r="T9" t="n">
         <v>-0.0747</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0224</v>
+        <v>0.056</v>
       </c>
       <c r="V9" t="n">
         <v>-1.7501</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3197</v>
+        <v>-2.3032</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2168</v>
+        <v>-2.3348</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1029</v>
+        <v>0.0316</v>
       </c>
       <c r="G10" t="n">
         <v>0.4592</v>
@@ -1234,13 +1234,13 @@
         <v>3.0154</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2996</v>
+        <v>-0.2831</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4086</v>
+        <v>-0.5265</v>
       </c>
       <c r="U10" t="n">
-        <v>0.109</v>
+        <v>0.2434</v>
       </c>
       <c r="V10" t="n">
         <v>0.5361</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4174</v>
+        <v>-4.2659</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9959</v>
+        <v>-2.8779</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4216</v>
+        <v>-1.388</v>
       </c>
       <c r="G11" t="n">
         <v>-0.5816</v>
@@ -1312,13 +1312,13 @@
         <v>1.1598</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6734</v>
+        <v>-0.5219</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5975</v>
+        <v>-0.4795</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.076</v>
+        <v>-0.0424</v>
       </c>
       <c r="V11" t="n">
         <v>-2.0026</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.7718</v>
+        <v>-7.4014</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.9934</v>
+        <v>-5.7575</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7784</v>
+        <v>-1.644</v>
       </c>
       <c r="G12" t="n">
         <v>-2.1423</v>
@@ -1390,13 +1390,13 @@
         <v>0.4639</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1502</v>
+        <v>0.2201</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2987</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1485</v>
+        <v>0.2829</v>
       </c>
       <c r="V12" t="n">
         <v>-1.0722</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.0882</v>
+        <v>-6.088200000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.023199999999999</v>
+        <v>-8.023299999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>1.934899999999999</v>
+        <v>1.935000000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-0.01449999999999951</v>
@@ -1468,13 +1468,13 @@
         <v>17.3967</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.07900000000000018</v>
+        <v>-0.07910000000000003</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.5365</v>
+        <v>-3.5364</v>
       </c>
       <c r="U13" t="n">
-        <v>3.4576</v>
+        <v>3.4573</v>
       </c>
       <c r="V13" t="n">
         <v>-1.355800000000001</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Y. OUATTARA</t>
+          <t>N. HIFI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.8477</v>
+        <v>2.9114</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.7083</v>
+        <v>4.8201</v>
       </c>
       <c r="F14" t="n">
-        <v>3.556</v>
+        <v>-1.9087</v>
       </c>
       <c r="G14" t="n">
-        <v>1.2772</v>
+        <v>1.2271</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7251</v>
+        <v>-0.1947</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5521</v>
+        <v>1.4218</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1236</v>
+        <v>3.3864</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6218</v>
+        <v>1.5397</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5018</v>
+        <v>1.8467</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1536</v>
+        <v>-2.1592</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1034</v>
+        <v>-1.7344</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0502</v>
+        <v>-0.4248</v>
       </c>
       <c r="P14" t="n">
-        <v>1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R14" t="n">
-        <v>2.5515</v>
+        <v>1.1598</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1788</v>
+        <v>0.0217</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6721</v>
+        <v>-0.1412</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8509</v>
+        <v>0.163</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>2.8223</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3.8945</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>N. HIFI</t>
+          <t>Y. OUATTARA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.7034</v>
+        <v>2.6797</v>
       </c>
       <c r="E15" t="n">
-        <v>4.7022</v>
+        <v>-0.7083</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.9987</v>
+        <v>3.388</v>
       </c>
       <c r="G15" t="n">
-        <v>1.2271</v>
+        <v>1.2772</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1947</v>
+        <v>0.7251</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4218</v>
+        <v>0.5521</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3864</v>
+        <v>1.1236</v>
       </c>
       <c r="K15" t="n">
-        <v>1.5397</v>
+        <v>0.6218</v>
       </c>
       <c r="L15" t="n">
-        <v>1.8467</v>
+        <v>0.5018</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.1592</v>
+        <v>0.1536</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.7344</v>
+        <v>0.1034</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4248</v>
+        <v>0.0502</v>
       </c>
       <c r="P15" t="n">
+        <v>1.3917</v>
+      </c>
+      <c r="Q15" t="n">
         <v>-1.1598</v>
       </c>
-      <c r="Q15" t="n">
-        <v>-2.3195</v>
-      </c>
       <c r="R15" t="n">
-        <v>1.1598</v>
+        <v>2.5515</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1863</v>
+        <v>0.0108</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2592</v>
+        <v>-0.6721</v>
       </c>
       <c r="U15" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.6829</v>
       </c>
       <c r="V15" t="n">
-        <v>2.8223</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>3.8945</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9478</v>
+        <v>1.8362</v>
       </c>
       <c r="E16" t="n">
         <v>-0.436</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3838</v>
+        <v>2.2722</v>
       </c>
       <c r="G16" t="n">
         <v>2.2981</v>
@@ -1702,13 +1702,13 @@
         <v>2.7834</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1705</v>
+        <v>0.0589</v>
       </c>
       <c r="T16" t="n">
         <v>-1.0455</v>
       </c>
       <c r="U16" t="n">
-        <v>1.216</v>
+        <v>1.1044</v>
       </c>
       <c r="V16" t="n">
         <v>-2.1444</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. SHAHRVIN</t>
+          <t>S. HERRERA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4298</v>
+        <v>1.2072</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9904</v>
+        <v>-1.3563</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5606</v>
+        <v>2.5635</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5555</v>
+        <v>0.925</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3145</v>
+        <v>1.3133</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2409</v>
+        <v>-0.3883</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5027</v>
+        <v>0.6249</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8401999999999999</v>
+        <v>1.378</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6625</v>
+        <v>-0.7531</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9473</v>
+        <v>0.3001</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5256999999999999</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4216</v>
+        <v>0.3648</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3917</v>
+        <v>2.7834</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5548</v>
+        <v>-0.2693</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4876</v>
+        <v>-0.8215</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0672</v>
+        <v>0.5522</v>
       </c>
       <c r="V17" t="n">
         <v>-1.0722</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. HERRERA</t>
+          <t>J. RHODEN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0056</v>
+        <v>1.1668</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3563</v>
+        <v>1.3423</v>
       </c>
       <c r="F18" t="n">
-        <v>2.3619</v>
+        <v>-0.1755</v>
       </c>
       <c r="G18" t="n">
-        <v>0.925</v>
+        <v>-0.5974</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3133</v>
+        <v>-2.6685</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3883</v>
+        <v>2.0711</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6249</v>
+        <v>1.6154</v>
       </c>
       <c r="K18" t="n">
-        <v>1.378</v>
+        <v>-0.9341</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7531</v>
+        <v>2.5495</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3001</v>
+        <v>-2.2127</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-1.7344</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3648</v>
+        <v>-0.4783</v>
       </c>
       <c r="P18" t="n">
-        <v>1.6237</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R18" t="n">
-        <v>2.7834</v>
+        <v>1.8556</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4709</v>
+        <v>0.0837</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8215</v>
+        <v>-0.098</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3506</v>
+        <v>0.1817</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0722</v>
+        <v>2.1444</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. ROBINSON</t>
+          <t>E. SHAHRVIN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6988</v>
+        <v>1.0588</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.4626</v>
+        <v>1.5186</v>
       </c>
       <c r="F19" t="n">
-        <v>4.1614</v>
+        <v>-0.4597</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9537</v>
+        <v>0.5555</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4921</v>
+        <v>0.3145</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4616</v>
+        <v>0.2409</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6964</v>
+        <v>1.5027</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0742</v>
+        <v>0.8401999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6222</v>
+        <v>0.6625</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2574</v>
+        <v>-0.9473</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4179</v>
+        <v>-0.5256999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1605</v>
+        <v>-0.4216</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3.2473</v>
+        <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1647</v>
+        <v>0.1838</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8215</v>
+        <v>0.0158</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.168</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1418</v>
+        <v>-1.0722</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. RHODEN</t>
+          <t>J. ROBINSON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6056</v>
+        <v>0.9176</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1064</v>
+        <v>-3.3447</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5008</v>
+        <v>4.2623</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5974</v>
+        <v>0.9537</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.6685</v>
+        <v>0.4921</v>
       </c>
       <c r="I20" t="n">
-        <v>2.0711</v>
+        <v>0.4616</v>
       </c>
       <c r="J20" t="n">
-        <v>1.6154</v>
+        <v>0.6964</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.9341</v>
+        <v>0.0742</v>
       </c>
       <c r="L20" t="n">
-        <v>2.5495</v>
+        <v>0.6222</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.2127</v>
+        <v>0.2574</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.7344</v>
+        <v>0.4179</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4783</v>
+        <v>-0.1605</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.4639</v>
+        <v>-0.232</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.3195</v>
+        <v>-3.4793</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8556</v>
+        <v>3.2473</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4775</v>
+        <v>0.054</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3339</v>
+        <v>-0.7035</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1436</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>2.1444</v>
+        <v>0.1418</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1444</v>
+        <v>0.1418</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. FAYE</t>
+          <t>A. M'BAYE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5189</v>
+        <v>0.0046</v>
       </c>
       <c r="E21" t="n">
-        <v>0.999</v>
+        <v>1.2572</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5178</v>
+        <v>-1.2525</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.3056</v>
+        <v>-2.536</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6097</v>
+        <v>-0.3745</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6959</v>
+        <v>-2.1616</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7354000000000001</v>
+        <v>0.0519</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5881999999999999</v>
+        <v>1.1595</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1472</v>
+        <v>-1.1077</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.041</v>
+        <v>-2.5879</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1979</v>
+        <v>-1.534</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8431</v>
+        <v>-1.0539</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.141</v>
+        <v>-0.0677</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2636</v>
+        <v>0.0788</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4046</v>
+        <v>-0.1465</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.2862</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. M'BAYE</t>
+          <t>M. FAYE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9219000000000001</v>
+        <v>-0.3001</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4315</v>
+        <v>1.1169</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3534</v>
+        <v>-1.417</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.536</v>
+        <v>-1.3056</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3745</v>
+        <v>-0.6097</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.1616</v>
+        <v>-0.6959</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0519</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>1.1595</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.1077</v>
+        <v>0.1472</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.5879</v>
+        <v>-2.041</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.534</v>
+        <v>-1.1979</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.0539</v>
+        <v>-0.8431</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9941</v>
+        <v>0.07779999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7468</v>
+        <v>0.3815</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2473</v>
+        <v>-0.3038</v>
       </c>
       <c r="V22" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2.2862</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.9734</v>
+        <v>-0.8218</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.9232</v>
+        <v>-0.8052</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0502</v>
+        <v>-0.0166</v>
       </c>
       <c r="G23" t="n">
         <v>-1.3103</v>
@@ -2248,13 +2248,13 @@
         <v>0.6959</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3589</v>
+        <v>-0.2074</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.224</v>
+        <v>-0.1061</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1349</v>
+        <v>-0.1013</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.2896</v>
+        <v>-1.334</v>
       </c>
       <c r="E24" t="n">
         <v>-3.5854</v>
       </c>
       <c r="F24" t="n">
-        <v>2.2958</v>
+        <v>2.2515</v>
       </c>
       <c r="G24" t="n">
         <v>1.5619</v>
@@ -2326,13 +2326,13 @@
         <v>2.0876</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1485</v>
+        <v>0.1041</v>
       </c>
       <c r="T24" t="n">
         <v>-0.8962</v>
       </c>
       <c r="U24" t="n">
-        <v>1.0447</v>
+        <v>1.0003</v>
       </c>
       <c r="V24" t="n">
         <v>-1.6083</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.4468</v>
+        <v>-2.4519</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.8344</v>
+        <v>-1.8959</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.6125</v>
+        <v>-0.556</v>
       </c>
       <c r="G25" t="n">
         <v>-3.0349</v>
@@ -2404,13 +2404,13 @@
         <v>0.9278</v>
       </c>
       <c r="S25" t="n">
-        <v>1.82</v>
+        <v>0.8149</v>
       </c>
       <c r="T25" t="n">
-        <v>1.6122</v>
+        <v>0.5507</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2078</v>
+        <v>0.2642</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>6.088099999999999</v>
+        <v>6.874499999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.0767</v>
+        <v>-2.076700000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>8.164899999999999</v>
+        <v>8.951499999999999</v>
       </c>
       <c r="G26" t="n">
         <v>0.01429999999999909</v>
@@ -2473,7 +2473,7 @@
         <v>-2.140400000000001</v>
       </c>
       <c r="P26" t="n">
-        <v>4.638999999999999</v>
+        <v>4.638999999999998</v>
       </c>
       <c r="Q26" t="n">
         <v>-17.3966</v>
@@ -2482,13 +2482,13 @@
         <v>22.0355</v>
       </c>
       <c r="S26" t="n">
-        <v>0.07920000000000038</v>
+        <v>0.8653</v>
       </c>
       <c r="T26" t="n">
         <v>-3.4573</v>
       </c>
       <c r="U26" t="n">
-        <v>3.5365</v>
+        <v>4.3227</v>
       </c>
       <c r="V26" t="n">
         <v>1.3558</v>
